--- a/data/ai_konstanten/health.xlsx
+++ b/data/ai_konstanten/health.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6092218aa314deb/Dokumente/hackerthon/ai/training_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6092218aa314deb/Dokumente/hackerthon/data/ai_konstanten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{C74F6FAA-9F9A-4FC4-BE34-46D1A99E7820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FB3BB2-A55F-4A34-9187-599B53AE6CF1}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{C74F6FAA-9F9A-4FC4-BE34-46D1A99E7820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4261BEA-72E6-4307-B391-DA563D307440}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" activeTab="1" xr2:uid="{D427C77A-E679-44B6-86BB-64B55F7FE4CF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="327">
   <si>
     <t>hour</t>
   </si>
@@ -1022,43 +1022,7 @@
     <t>type</t>
   </si>
   <si>
-    <t>duration_1</t>
-  </si>
-  <si>
-    <t>duration_2</t>
-  </si>
-  <si>
-    <t>duration_3</t>
-  </si>
-  <si>
-    <t>duration_4</t>
-  </si>
-  <si>
-    <t>duration_5</t>
-  </si>
-  <si>
-    <t>duration_6</t>
-  </si>
-  <si>
-    <t>duration_7</t>
-  </si>
-  <si>
-    <t>duration_8</t>
-  </si>
-  <si>
-    <t>duration_9</t>
-  </si>
-  <si>
-    <t>duration_10</t>
-  </si>
-  <si>
-    <t>duration_ex</t>
-  </si>
-  <si>
     <t>Healthiness_Score (1-100)</t>
-  </si>
-  <si>
-    <t>Healthy_Label (0=healthy,1=unhealthy)</t>
   </si>
 </sst>
 </file>
@@ -1197,6 +1161,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1641,6 +1609,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1658,7 +1627,7 @@
     <col min="12" max="12" width="33.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="56" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="28" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -1690,11 +1659,9 @@
         <v>13</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>338</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -1730,9 +1697,6 @@
       <c r="K2">
         <v>44</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
@@ -1768,9 +1732,6 @@
       <c r="K3">
         <v>42</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
@@ -1806,9 +1767,6 @@
       <c r="K4">
         <v>46</v>
       </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
@@ -1844,9 +1802,6 @@
       <c r="K5">
         <v>52</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
@@ -1882,9 +1837,6 @@
       <c r="K6">
         <v>46</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
@@ -1920,9 +1872,6 @@
       <c r="K7">
         <v>51</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
@@ -1958,9 +1907,6 @@
       <c r="K8">
         <v>31</v>
       </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
@@ -1996,9 +1942,6 @@
       <c r="K9">
         <v>57</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
@@ -2034,9 +1977,6 @@
       <c r="K10">
         <v>66</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
@@ -2072,9 +2012,6 @@
       <c r="K11">
         <v>50</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
@@ -2110,9 +2047,6 @@
       <c r="K12">
         <v>64</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
@@ -2148,9 +2082,6 @@
       <c r="K13">
         <v>41</v>
       </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
@@ -2186,9 +2117,6 @@
       <c r="K14">
         <v>46</v>
       </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
@@ -2224,9 +2152,6 @@
       <c r="K15">
         <v>49</v>
       </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
@@ -2262,11 +2187,8 @@
       <c r="K16">
         <v>40</v>
       </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>30</v>
       </c>
@@ -2300,11 +2222,8 @@
       <c r="K17">
         <v>43</v>
       </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>31</v>
       </c>
@@ -2338,11 +2257,8 @@
       <c r="K18">
         <v>41</v>
       </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>32</v>
       </c>
@@ -2376,11 +2292,8 @@
       <c r="K19">
         <v>53</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>33</v>
       </c>
@@ -2414,11 +2327,8 @@
       <c r="K20">
         <v>44</v>
       </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>34</v>
       </c>
@@ -2452,11 +2362,8 @@
       <c r="K21">
         <v>42</v>
       </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>35</v>
       </c>
@@ -2490,11 +2397,8 @@
       <c r="K22">
         <v>49</v>
       </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
@@ -2528,11 +2432,8 @@
       <c r="K23">
         <v>46</v>
       </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
@@ -2566,11 +2467,8 @@
       <c r="K24">
         <v>37</v>
       </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>38</v>
       </c>
@@ -2604,11 +2502,8 @@
       <c r="K25">
         <v>6</v>
       </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
@@ -2642,11 +2537,8 @@
       <c r="K26">
         <v>5</v>
       </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>40</v>
       </c>
@@ -2680,11 +2572,8 @@
       <c r="K27">
         <v>57</v>
       </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
@@ -2718,11 +2607,8 @@
       <c r="K28">
         <v>57</v>
       </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>42</v>
       </c>
@@ -2756,11 +2642,8 @@
       <c r="K29">
         <v>63</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>43</v>
       </c>
@@ -2794,11 +2677,8 @@
       <c r="K30">
         <v>47</v>
       </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>44</v>
       </c>
@@ -2832,11 +2712,8 @@
       <c r="K31">
         <v>57</v>
       </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>45</v>
       </c>
@@ -2870,11 +2747,8 @@
       <c r="K32">
         <v>71</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>47</v>
       </c>
@@ -2908,11 +2782,8 @@
       <c r="K33">
         <v>67</v>
       </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>48</v>
       </c>
@@ -2946,11 +2817,8 @@
       <c r="K34">
         <v>62</v>
       </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>49</v>
       </c>
@@ -2984,11 +2852,8 @@
       <c r="K35">
         <v>59</v>
       </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>50</v>
       </c>
@@ -3022,11 +2887,8 @@
       <c r="K36">
         <v>53</v>
       </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>51</v>
       </c>
@@ -3060,11 +2922,8 @@
       <c r="K37">
         <v>66</v>
       </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>52</v>
       </c>
@@ -3098,11 +2957,8 @@
       <c r="K38">
         <v>65</v>
       </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>53</v>
       </c>
@@ -3136,11 +2992,8 @@
       <c r="K39">
         <v>59</v>
       </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>54</v>
       </c>
@@ -3174,11 +3027,8 @@
       <c r="K40">
         <v>58</v>
       </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>55</v>
       </c>
@@ -3212,11 +3062,8 @@
       <c r="K41">
         <v>74</v>
       </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>56</v>
       </c>
@@ -3250,11 +3097,8 @@
       <c r="K42">
         <v>75</v>
       </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>57</v>
       </c>
@@ -3288,11 +3132,8 @@
       <c r="K43">
         <v>68</v>
       </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>58</v>
       </c>
@@ -3326,11 +3167,8 @@
       <c r="K44">
         <v>62</v>
       </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>59</v>
       </c>
@@ -3364,11 +3202,8 @@
       <c r="K45">
         <v>67</v>
       </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>60</v>
       </c>
@@ -3402,11 +3237,8 @@
       <c r="K46">
         <v>61</v>
       </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>61</v>
       </c>
@@ -3440,11 +3272,8 @@
       <c r="K47">
         <v>59</v>
       </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>62</v>
       </c>
@@ -3478,11 +3307,8 @@
       <c r="K48">
         <v>71</v>
       </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>63</v>
       </c>
@@ -3516,11 +3342,8 @@
       <c r="K49">
         <v>61</v>
       </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>64</v>
       </c>
@@ -3554,11 +3377,8 @@
       <c r="K50">
         <v>58</v>
       </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>65</v>
       </c>
@@ -3592,11 +3412,8 @@
       <c r="K51">
         <v>52</v>
       </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>66</v>
       </c>
@@ -3630,11 +3447,8 @@
       <c r="K52">
         <v>65</v>
       </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>67</v>
       </c>
@@ -3668,11 +3482,8 @@
       <c r="K53">
         <v>61</v>
       </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>68</v>
       </c>
@@ -3706,11 +3517,8 @@
       <c r="K54">
         <v>60</v>
       </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>69</v>
       </c>
@@ -3744,11 +3552,8 @@
       <c r="K55">
         <v>57</v>
       </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>70</v>
       </c>
@@ -3782,11 +3587,8 @@
       <c r="K56">
         <v>57</v>
       </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>71</v>
       </c>
@@ -3820,11 +3622,8 @@
       <c r="K57">
         <v>65</v>
       </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>72</v>
       </c>
@@ -3858,11 +3657,8 @@
       <c r="K58">
         <v>61</v>
       </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>73</v>
       </c>
@@ -3896,11 +3692,8 @@
       <c r="K59">
         <v>58</v>
       </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>74</v>
       </c>
@@ -3934,11 +3727,8 @@
       <c r="K60">
         <v>66</v>
       </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>75</v>
       </c>
@@ -3972,11 +3762,8 @@
       <c r="K61">
         <v>63</v>
       </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>76</v>
       </c>
@@ -4010,11 +3797,8 @@
       <c r="K62">
         <v>55</v>
       </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>77</v>
       </c>
@@ -4048,11 +3832,8 @@
       <c r="K63">
         <v>50</v>
       </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>78</v>
       </c>
@@ -4086,11 +3867,8 @@
       <c r="K64">
         <v>65</v>
       </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>80</v>
       </c>
@@ -4124,11 +3902,8 @@
       <c r="K65">
         <v>50</v>
       </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>81</v>
       </c>
@@ -4162,11 +3937,8 @@
       <c r="K66">
         <v>64</v>
       </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>82</v>
       </c>
@@ -4200,11 +3972,8 @@
       <c r="K67">
         <v>61</v>
       </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>83</v>
       </c>
@@ -4238,11 +4007,8 @@
       <c r="K68">
         <v>54</v>
       </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>84</v>
       </c>
@@ -4276,11 +4042,8 @@
       <c r="K69">
         <v>47</v>
       </c>
-      <c r="L69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>85</v>
       </c>
@@ -4314,11 +4077,8 @@
       <c r="K70">
         <v>55</v>
       </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>86</v>
       </c>
@@ -4352,11 +4112,8 @@
       <c r="K71">
         <v>78</v>
       </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>87</v>
       </c>
@@ -4390,11 +4147,8 @@
       <c r="K72">
         <v>63</v>
       </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>88</v>
       </c>
@@ -4428,11 +4182,8 @@
       <c r="K73">
         <v>53</v>
       </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>89</v>
       </c>
@@ -4466,11 +4217,8 @@
       <c r="K74">
         <v>62</v>
       </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>90</v>
       </c>
@@ -4504,11 +4252,8 @@
       <c r="K75">
         <v>59</v>
       </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>91</v>
       </c>
@@ -4542,11 +4287,8 @@
       <c r="K76">
         <v>45</v>
       </c>
-      <c r="L76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>92</v>
       </c>
@@ -4580,11 +4322,8 @@
       <c r="K77">
         <v>40</v>
       </c>
-      <c r="L77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>93</v>
       </c>
@@ -4618,11 +4357,8 @@
       <c r="K78">
         <v>37</v>
       </c>
-      <c r="L78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>94</v>
       </c>
@@ -4656,11 +4392,8 @@
       <c r="K79">
         <v>51</v>
       </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>95</v>
       </c>
@@ -4694,11 +4427,8 @@
       <c r="K80">
         <v>51</v>
       </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>96</v>
       </c>
@@ -4732,11 +4462,8 @@
       <c r="K81">
         <v>74</v>
       </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>97</v>
       </c>
@@ -4770,11 +4497,8 @@
       <c r="K82">
         <v>77</v>
       </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>99</v>
       </c>
@@ -4808,11 +4532,8 @@
       <c r="K83">
         <v>72</v>
       </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>100</v>
       </c>
@@ -4846,11 +4567,8 @@
       <c r="K84">
         <v>76</v>
       </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>101</v>
       </c>
@@ -4884,11 +4602,8 @@
       <c r="K85">
         <v>79</v>
       </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>102</v>
       </c>
@@ -4922,11 +4637,8 @@
       <c r="K86">
         <v>76</v>
       </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>103</v>
       </c>
@@ -4960,11 +4672,8 @@
       <c r="K87">
         <v>74</v>
       </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>104</v>
       </c>
@@ -4998,11 +4707,8 @@
       <c r="K88">
         <v>58</v>
       </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>105</v>
       </c>
@@ -5036,11 +4742,8 @@
       <c r="K89">
         <v>73</v>
       </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>106</v>
       </c>
@@ -5074,11 +4777,8 @@
       <c r="K90">
         <v>72</v>
       </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
         <v>107</v>
       </c>
@@ -5112,11 +4812,8 @@
       <c r="K91">
         <v>70</v>
       </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>109</v>
       </c>
@@ -5150,11 +4847,8 @@
       <c r="K92">
         <v>49</v>
       </c>
-      <c r="L92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>110</v>
       </c>
@@ -5188,11 +4882,8 @@
       <c r="K93">
         <v>55</v>
       </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>111</v>
       </c>
@@ -5226,11 +4917,8 @@
       <c r="K94">
         <v>47</v>
       </c>
-      <c r="L94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>112</v>
       </c>
@@ -5264,11 +4952,8 @@
       <c r="K95">
         <v>63</v>
       </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>113</v>
       </c>
@@ -5302,11 +4987,8 @@
       <c r="K96">
         <v>47</v>
       </c>
-      <c r="L96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>114</v>
       </c>
@@ -5340,11 +5022,8 @@
       <c r="K97">
         <v>64</v>
       </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>115</v>
       </c>
@@ -5378,11 +5057,8 @@
       <c r="K98">
         <v>49</v>
       </c>
-      <c r="L98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>116</v>
       </c>
@@ -5416,11 +5092,8 @@
       <c r="K99">
         <v>95</v>
       </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>117</v>
       </c>
@@ -5454,11 +5127,8 @@
       <c r="K100">
         <v>91</v>
       </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
         <v>118</v>
       </c>
@@ -5492,11 +5162,8 @@
       <c r="K101">
         <v>61</v>
       </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>119</v>
       </c>
@@ -5530,11 +5197,8 @@
       <c r="K102">
         <v>69</v>
       </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>120</v>
       </c>
@@ -5568,11 +5232,8 @@
       <c r="K103">
         <v>68</v>
       </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>121</v>
       </c>
@@ -5606,11 +5267,8 @@
       <c r="K104">
         <v>46</v>
       </c>
-      <c r="L104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>122</v>
       </c>
@@ -5644,11 +5302,8 @@
       <c r="K105">
         <v>45</v>
       </c>
-      <c r="L105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>124</v>
       </c>
@@ -5682,11 +5337,8 @@
       <c r="K106">
         <v>47</v>
       </c>
-      <c r="L106">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>125</v>
       </c>
@@ -5720,11 +5372,8 @@
       <c r="K107">
         <v>46</v>
       </c>
-      <c r="L107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>126</v>
       </c>
@@ -5758,11 +5407,8 @@
       <c r="K108">
         <v>51</v>
       </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>127</v>
       </c>
@@ -5796,11 +5442,8 @@
       <c r="K109">
         <v>56</v>
       </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
         <v>128</v>
       </c>
@@ -5834,11 +5477,8 @@
       <c r="K110">
         <v>54</v>
       </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
         <v>129</v>
       </c>
@@ -5872,11 +5512,8 @@
       <c r="K111">
         <v>48</v>
       </c>
-      <c r="L111">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>130</v>
       </c>
@@ -5910,11 +5547,8 @@
       <c r="K112">
         <v>29</v>
       </c>
-      <c r="L112">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>131</v>
       </c>
@@ -5948,11 +5582,8 @@
       <c r="K113">
         <v>15</v>
       </c>
-      <c r="L113">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
         <v>132</v>
       </c>
@@ -5986,11 +5617,8 @@
       <c r="K114">
         <v>31</v>
       </c>
-      <c r="L114">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
         <v>133</v>
       </c>
@@ -6024,11 +5652,8 @@
       <c r="K115">
         <v>56</v>
       </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
         <v>134</v>
       </c>
@@ -6062,11 +5687,8 @@
       <c r="K116">
         <v>54</v>
       </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>135</v>
       </c>
@@ -6100,11 +5722,8 @@
       <c r="K117">
         <v>68</v>
       </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>136</v>
       </c>
@@ -6138,11 +5757,8 @@
       <c r="K118">
         <v>44</v>
       </c>
-      <c r="L118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
         <v>137</v>
       </c>
@@ -6176,11 +5792,8 @@
       <c r="K119">
         <v>52</v>
       </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
         <v>138</v>
       </c>
@@ -6214,11 +5827,8 @@
       <c r="K120">
         <v>52</v>
       </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
         <v>139</v>
       </c>
@@ -6252,11 +5862,8 @@
       <c r="K121">
         <v>54</v>
       </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>140</v>
       </c>
@@ -6290,11 +5897,8 @@
       <c r="K122">
         <v>48</v>
       </c>
-      <c r="L122">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>141</v>
       </c>
@@ -6328,11 +5932,8 @@
       <c r="K123">
         <v>69</v>
       </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>143</v>
       </c>
@@ -6366,11 +5967,8 @@
       <c r="K124">
         <v>63</v>
       </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>144</v>
       </c>
@@ -6404,11 +6002,8 @@
       <c r="K125">
         <v>68</v>
       </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>145</v>
       </c>
@@ -6442,11 +6037,8 @@
       <c r="K126">
         <v>67</v>
       </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
         <v>146</v>
       </c>
@@ -6480,11 +6072,8 @@
       <c r="K127">
         <v>60</v>
       </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
         <v>147</v>
       </c>
@@ -6518,11 +6107,8 @@
       <c r="K128">
         <v>66</v>
       </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
         <v>148</v>
       </c>
@@ -6556,11 +6142,8 @@
       <c r="K129">
         <v>54</v>
       </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>149</v>
       </c>
@@ -6594,11 +6177,8 @@
       <c r="K130">
         <v>60</v>
       </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>150</v>
       </c>
@@ -6632,11 +6212,8 @@
       <c r="K131">
         <v>67</v>
       </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>151</v>
       </c>
@@ -6670,11 +6247,8 @@
       <c r="K132">
         <v>67</v>
       </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>152</v>
       </c>
@@ -6708,11 +6282,8 @@
       <c r="K133">
         <v>48</v>
       </c>
-      <c r="L133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
         <v>153</v>
       </c>
@@ -6746,11 +6317,8 @@
       <c r="K134">
         <v>63</v>
       </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
         <v>154</v>
       </c>
@@ -6784,11 +6352,8 @@
       <c r="K135">
         <v>47</v>
       </c>
-      <c r="L135">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>155</v>
       </c>
@@ -6822,11 +6387,8 @@
       <c r="K136">
         <v>32</v>
       </c>
-      <c r="L136">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
         <v>156</v>
       </c>
@@ -6860,11 +6422,8 @@
       <c r="K137">
         <v>42</v>
       </c>
-      <c r="L137">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
         <v>157</v>
       </c>
@@ -6898,11 +6457,8 @@
       <c r="K138">
         <v>49</v>
       </c>
-      <c r="L138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
         <v>158</v>
       </c>
@@ -6936,11 +6492,8 @@
       <c r="K139">
         <v>69</v>
       </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>160</v>
       </c>
@@ -6974,11 +6527,8 @@
       <c r="K140">
         <v>76</v>
       </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
         <v>161</v>
       </c>
@@ -7012,11 +6562,8 @@
       <c r="K141">
         <v>75</v>
       </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
         <v>162</v>
       </c>
@@ -7050,11 +6597,8 @@
       <c r="K142">
         <v>70</v>
       </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
         <v>163</v>
       </c>
@@ -7088,11 +6632,8 @@
       <c r="K143">
         <v>71</v>
       </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
         <v>164</v>
       </c>
@@ -7126,11 +6667,8 @@
       <c r="K144">
         <v>69</v>
       </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
         <v>165</v>
       </c>
@@ -7164,11 +6702,8 @@
       <c r="K145">
         <v>67</v>
       </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
         <v>166</v>
       </c>
@@ -7202,11 +6737,8 @@
       <c r="K146">
         <v>75</v>
       </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
         <v>167</v>
       </c>
@@ -7240,11 +6772,8 @@
       <c r="K147">
         <v>76</v>
       </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
         <v>168</v>
       </c>
@@ -7278,11 +6807,8 @@
       <c r="K148">
         <v>68</v>
       </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
         <v>169</v>
       </c>
@@ -7316,11 +6842,8 @@
       <c r="K149">
         <v>73</v>
       </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
         <v>170</v>
       </c>
@@ -7354,11 +6877,8 @@
       <c r="K150">
         <v>72</v>
       </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
         <v>171</v>
       </c>
@@ -7392,11 +6912,8 @@
       <c r="K151">
         <v>61</v>
       </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
         <v>173</v>
       </c>
@@ -7430,11 +6947,8 @@
       <c r="K152">
         <v>59</v>
       </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
         <v>174</v>
       </c>
@@ -7468,11 +6982,8 @@
       <c r="K153">
         <v>59</v>
       </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="5" t="s">
         <v>175</v>
       </c>
@@ -7506,11 +7017,8 @@
       <c r="K154">
         <v>59</v>
       </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
         <v>176</v>
       </c>
@@ -7544,11 +7052,8 @@
       <c r="K155">
         <v>12</v>
       </c>
-      <c r="L155">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
         <v>178</v>
       </c>
@@ -7582,11 +7087,8 @@
       <c r="K156">
         <v>11</v>
       </c>
-      <c r="L156">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
         <v>179</v>
       </c>
@@ -7620,11 +7122,8 @@
       <c r="K157">
         <v>11</v>
       </c>
-      <c r="L157">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
         <v>180</v>
       </c>
@@ -7658,11 +7157,8 @@
       <c r="K158">
         <v>11</v>
       </c>
-      <c r="L158">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
         <v>181</v>
       </c>
@@ -7696,11 +7192,8 @@
       <c r="K159">
         <v>15</v>
       </c>
-      <c r="L159">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
         <v>182</v>
       </c>
@@ -7734,11 +7227,8 @@
       <c r="K160">
         <v>4</v>
       </c>
-      <c r="L160">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
         <v>184</v>
       </c>
@@ -7772,11 +7262,8 @@
       <c r="K161">
         <v>8</v>
       </c>
-      <c r="L161">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
         <v>185</v>
       </c>
@@ -7810,11 +7297,8 @@
       <c r="K162">
         <v>7</v>
       </c>
-      <c r="L162">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
         <v>186</v>
       </c>
@@ -7848,11 +7332,8 @@
       <c r="K163">
         <v>39</v>
       </c>
-      <c r="L163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
         <v>187</v>
       </c>
@@ -7886,11 +7367,8 @@
       <c r="K164">
         <v>9</v>
       </c>
-      <c r="L164">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
         <v>188</v>
       </c>
@@ -7924,11 +7402,8 @@
       <c r="K165">
         <v>12</v>
       </c>
-      <c r="L165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
         <v>189</v>
       </c>
@@ -7962,11 +7437,8 @@
       <c r="K166">
         <v>3</v>
       </c>
-      <c r="L166">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
         <v>190</v>
       </c>
@@ -8000,11 +7472,8 @@
       <c r="K167">
         <v>2</v>
       </c>
-      <c r="L167">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
         <v>191</v>
       </c>
@@ -8038,11 +7507,8 @@
       <c r="K168">
         <v>4</v>
       </c>
-      <c r="L168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
         <v>192</v>
       </c>
@@ -8076,11 +7542,8 @@
       <c r="K169">
         <v>4</v>
       </c>
-      <c r="L169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
         <v>193</v>
       </c>
@@ -8114,11 +7577,8 @@
       <c r="K170">
         <v>19</v>
       </c>
-      <c r="L170">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
         <v>194</v>
       </c>
@@ -8152,11 +7612,8 @@
       <c r="K171">
         <v>28</v>
       </c>
-      <c r="L171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
         <v>195</v>
       </c>
@@ -8190,11 +7647,8 @@
       <c r="K172">
         <v>54</v>
       </c>
-      <c r="L172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
         <v>196</v>
       </c>
@@ -8228,11 +7682,8 @@
       <c r="K173">
         <v>38</v>
       </c>
-      <c r="L173">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
         <v>197</v>
       </c>
@@ -8266,11 +7717,8 @@
       <c r="K174">
         <v>51</v>
       </c>
-      <c r="L174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
         <v>199</v>
       </c>
@@ -8304,11 +7752,8 @@
       <c r="K175">
         <v>46</v>
       </c>
-      <c r="L175">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="5" t="s">
         <v>200</v>
       </c>
@@ -8342,11 +7787,8 @@
       <c r="K176">
         <v>45</v>
       </c>
-      <c r="L176">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
         <v>201</v>
       </c>
@@ -8380,11 +7822,8 @@
       <c r="K177">
         <v>55</v>
       </c>
-      <c r="L177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="5" t="s">
         <v>202</v>
       </c>
@@ -8418,11 +7857,8 @@
       <c r="K178">
         <v>49</v>
       </c>
-      <c r="L178">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="5" t="s">
         <v>203</v>
       </c>
@@ -8456,11 +7892,8 @@
       <c r="K179">
         <v>53</v>
       </c>
-      <c r="L179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="5" t="s">
         <v>204</v>
       </c>
@@ -8494,11 +7927,8 @@
       <c r="K180">
         <v>41</v>
       </c>
-      <c r="L180">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="5" t="s">
         <v>205</v>
       </c>
@@ -8532,11 +7962,8 @@
       <c r="K181">
         <v>50</v>
       </c>
-      <c r="L181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="5" t="s">
         <v>206</v>
       </c>
@@ -8570,11 +7997,8 @@
       <c r="K182">
         <v>54</v>
       </c>
-      <c r="L182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
         <v>207</v>
       </c>
@@ -8608,11 +8032,8 @@
       <c r="K183">
         <v>47</v>
       </c>
-      <c r="L183">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="5" t="s">
         <v>208</v>
       </c>
@@ -8646,11 +8067,8 @@
       <c r="K184">
         <v>43</v>
       </c>
-      <c r="L184">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
         <v>210</v>
       </c>
@@ -8684,11 +8102,8 @@
       <c r="K185">
         <v>43</v>
       </c>
-      <c r="L185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
         <v>211</v>
       </c>
@@ -8722,11 +8137,8 @@
       <c r="K186">
         <v>34</v>
       </c>
-      <c r="L186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="5" t="s">
         <v>212</v>
       </c>
@@ -8760,11 +8172,8 @@
       <c r="K187">
         <v>29</v>
       </c>
-      <c r="L187">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" s="5" t="s">
         <v>213</v>
       </c>
@@ -8798,11 +8207,8 @@
       <c r="K188">
         <v>31</v>
       </c>
-      <c r="L188">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" s="5" t="s">
         <v>214</v>
       </c>
@@ -8836,11 +8242,8 @@
       <c r="K189">
         <v>29</v>
       </c>
-      <c r="L189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="5" t="s">
         <v>215</v>
       </c>
@@ -8874,11 +8277,8 @@
       <c r="K190">
         <v>43</v>
       </c>
-      <c r="L190">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" s="5" t="s">
         <v>216</v>
       </c>
@@ -8912,11 +8312,8 @@
       <c r="K191">
         <v>42</v>
       </c>
-      <c r="L191">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" s="5" t="s">
         <v>217</v>
       </c>
@@ -8950,11 +8347,8 @@
       <c r="K192">
         <v>46</v>
       </c>
-      <c r="L192">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" s="5" t="s">
         <v>218</v>
       </c>
@@ -8988,11 +8382,8 @@
       <c r="K193">
         <v>46</v>
       </c>
-      <c r="L193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" s="5" t="s">
         <v>219</v>
       </c>
@@ -9026,11 +8417,8 @@
       <c r="K194">
         <v>49</v>
       </c>
-      <c r="L194">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" s="5" t="s">
         <v>220</v>
       </c>
@@ -9064,11 +8452,8 @@
       <c r="K195">
         <v>44</v>
       </c>
-      <c r="L195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" s="5" t="s">
         <v>221</v>
       </c>
@@ -9102,11 +8487,8 @@
       <c r="K196">
         <v>53</v>
       </c>
-      <c r="L196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" s="5" t="s">
         <v>222</v>
       </c>
@@ -9140,11 +8522,8 @@
       <c r="K197">
         <v>40</v>
       </c>
-      <c r="L197">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" s="5" t="s">
         <v>223</v>
       </c>
@@ -9178,11 +8557,8 @@
       <c r="K198">
         <v>71</v>
       </c>
-      <c r="L198">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="5" t="s">
         <v>225</v>
       </c>
@@ -9216,11 +8592,8 @@
       <c r="K199">
         <v>67</v>
       </c>
-      <c r="L199">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="5" t="s">
         <v>226</v>
       </c>
@@ -9254,11 +8627,8 @@
       <c r="K200">
         <v>61</v>
       </c>
-      <c r="L200">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
         <v>227</v>
       </c>
@@ -9292,11 +8662,8 @@
       <c r="K201">
         <v>43</v>
       </c>
-      <c r="L201">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="5" t="s">
         <v>228</v>
       </c>
@@ -9330,11 +8697,8 @@
       <c r="K202">
         <v>52</v>
       </c>
-      <c r="L202">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="5" t="s">
         <v>229</v>
       </c>
@@ -9368,11 +8732,8 @@
       <c r="K203">
         <v>20</v>
       </c>
-      <c r="L203">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" s="5" t="s">
         <v>230</v>
       </c>
@@ -9406,11 +8767,8 @@
       <c r="K204">
         <v>15</v>
       </c>
-      <c r="L204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
         <v>231</v>
       </c>
@@ -9444,11 +8802,8 @@
       <c r="K205">
         <v>52</v>
       </c>
-      <c r="L205">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" s="5" t="s">
         <v>232</v>
       </c>
@@ -9482,11 +8837,8 @@
       <c r="K206">
         <v>44</v>
       </c>
-      <c r="L206">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" s="5" t="s">
         <v>233</v>
       </c>
@@ -9520,11 +8872,8 @@
       <c r="K207">
         <v>36</v>
       </c>
-      <c r="L207">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" s="5" t="s">
         <v>234</v>
       </c>
@@ -9558,11 +8907,8 @@
       <c r="K208">
         <v>59</v>
       </c>
-      <c r="L208">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="5" t="s">
         <v>235</v>
       </c>
@@ -9596,11 +8942,8 @@
       <c r="K209">
         <v>55</v>
       </c>
-      <c r="L209">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="5" t="s">
         <v>236</v>
       </c>
@@ -9634,11 +8977,8 @@
       <c r="K210">
         <v>65</v>
       </c>
-      <c r="L210">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="5" t="s">
         <v>237</v>
       </c>
@@ -9672,11 +9012,8 @@
       <c r="K211">
         <v>58</v>
       </c>
-      <c r="L211">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
         <v>238</v>
       </c>
@@ -9710,11 +9047,8 @@
       <c r="K212">
         <v>58</v>
       </c>
-      <c r="L212">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="5" t="s">
         <v>239</v>
       </c>
@@ -9748,11 +9082,8 @@
       <c r="K213">
         <v>59</v>
       </c>
-      <c r="L213">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="5" t="s">
         <v>240</v>
       </c>
@@ -9786,11 +9117,8 @@
       <c r="K214">
         <v>60</v>
       </c>
-      <c r="L214">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" s="5" t="s">
         <v>241</v>
       </c>
@@ -9824,11 +9152,8 @@
       <c r="K215">
         <v>57</v>
       </c>
-      <c r="L215">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" s="5" t="s">
         <v>242</v>
       </c>
@@ -9862,11 +9187,8 @@
       <c r="K216">
         <v>58</v>
       </c>
-      <c r="L216">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" s="5" t="s">
         <v>243</v>
       </c>
@@ -9900,11 +9222,8 @@
       <c r="K217">
         <v>65</v>
       </c>
-      <c r="L217">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" s="5" t="s">
         <v>244</v>
       </c>
@@ -9938,11 +9257,8 @@
       <c r="K218">
         <v>67</v>
       </c>
-      <c r="L218">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" s="5" t="s">
         <v>245</v>
       </c>
@@ -9976,11 +9292,8 @@
       <c r="K219">
         <v>67</v>
       </c>
-      <c r="L219">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" s="5" t="s">
         <v>246</v>
       </c>
@@ -10014,11 +9327,8 @@
       <c r="K220">
         <v>70</v>
       </c>
-      <c r="L220">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" s="5" t="s">
         <v>247</v>
       </c>
@@ -10052,11 +9362,8 @@
       <c r="K221">
         <v>64</v>
       </c>
-      <c r="L221">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" s="5" t="s">
         <v>248</v>
       </c>
@@ -10090,11 +9397,8 @@
       <c r="K222">
         <v>58</v>
       </c>
-      <c r="L222">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" s="5" t="s">
         <v>249</v>
       </c>
@@ -10128,11 +9432,8 @@
       <c r="K223">
         <v>64</v>
       </c>
-      <c r="L223">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" s="5" t="s">
         <v>250</v>
       </c>
@@ -10166,11 +9467,8 @@
       <c r="K224">
         <v>56</v>
       </c>
-      <c r="L224">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A225" s="5" t="s">
         <v>251</v>
       </c>
@@ -10204,11 +9502,8 @@
       <c r="K225">
         <v>63</v>
       </c>
-      <c r="L225">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A226" s="5" t="s">
         <v>252</v>
       </c>
@@ -10242,11 +9537,8 @@
       <c r="K226">
         <v>58</v>
       </c>
-      <c r="L226">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A227" s="5" t="s">
         <v>253</v>
       </c>
@@ -10280,11 +9572,8 @@
       <c r="K227">
         <v>65</v>
       </c>
-      <c r="L227">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A228" s="5" t="s">
         <v>254</v>
       </c>
@@ -10318,11 +9607,8 @@
       <c r="K228">
         <v>50</v>
       </c>
-      <c r="L228">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" s="5" t="s">
         <v>255</v>
       </c>
@@ -10356,11 +9642,8 @@
       <c r="K229">
         <v>67</v>
       </c>
-      <c r="L229">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" s="5" t="s">
         <v>256</v>
       </c>
@@ -10394,11 +9677,8 @@
       <c r="K230">
         <v>52</v>
       </c>
-      <c r="L230">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" s="5" t="s">
         <v>257</v>
       </c>
@@ -10432,11 +9712,8 @@
       <c r="K231">
         <v>48</v>
       </c>
-      <c r="L231">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A232" s="5" t="s">
         <v>258</v>
       </c>
@@ -10470,11 +9747,8 @@
       <c r="K232">
         <v>52</v>
       </c>
-      <c r="L232">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A233" s="5" t="s">
         <v>259</v>
       </c>
@@ -10508,11 +9782,8 @@
       <c r="K233">
         <v>51</v>
       </c>
-      <c r="L233">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A234" s="5" t="s">
         <v>260</v>
       </c>
@@ -10546,11 +9817,8 @@
       <c r="K234">
         <v>53</v>
       </c>
-      <c r="L234">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A235" s="5" t="s">
         <v>261</v>
       </c>
@@ -10584,11 +9852,8 @@
       <c r="K235">
         <v>51</v>
       </c>
-      <c r="L235">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A236" s="5" t="s">
         <v>262</v>
       </c>
@@ -10622,11 +9887,8 @@
       <c r="K236">
         <v>48</v>
       </c>
-      <c r="L236">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A237" s="5" t="s">
         <v>263</v>
       </c>
@@ -10660,11 +9922,8 @@
       <c r="K237">
         <v>62</v>
       </c>
-      <c r="L237">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" s="5" t="s">
         <v>264</v>
       </c>
@@ -10698,11 +9957,8 @@
       <c r="K238">
         <v>60</v>
       </c>
-      <c r="L238">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" s="5" t="s">
         <v>265</v>
       </c>
@@ -10736,11 +9992,8 @@
       <c r="K239">
         <v>55</v>
       </c>
-      <c r="L239">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" s="5" t="s">
         <v>266</v>
       </c>
@@ -10774,11 +10027,8 @@
       <c r="K240">
         <v>98</v>
       </c>
-      <c r="L240">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" s="5" t="s">
         <v>267</v>
       </c>
@@ -10812,11 +10062,8 @@
       <c r="K241">
         <v>74</v>
       </c>
-      <c r="L241">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" s="5" t="s">
         <v>268</v>
       </c>
@@ -10850,11 +10097,8 @@
       <c r="K242">
         <v>72</v>
       </c>
-      <c r="L242">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A243" s="5" t="s">
         <v>269</v>
       </c>
@@ -10888,11 +10132,8 @@
       <c r="K243">
         <v>73</v>
       </c>
-      <c r="L243">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A244" s="5" t="s">
         <v>270</v>
       </c>
@@ -10926,11 +10167,8 @@
       <c r="K244">
         <v>69</v>
       </c>
-      <c r="L244">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A245" s="5" t="s">
         <v>271</v>
       </c>
@@ -10964,11 +10202,8 @@
       <c r="K245">
         <v>34</v>
       </c>
-      <c r="L245">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A246" s="5" t="s">
         <v>272</v>
       </c>
@@ -11002,11 +10237,8 @@
       <c r="K246">
         <v>40</v>
       </c>
-      <c r="L246">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A247" s="5" t="s">
         <v>273</v>
       </c>
@@ -11040,11 +10272,8 @@
       <c r="K247">
         <v>34</v>
       </c>
-      <c r="L247">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A248" s="5" t="s">
         <v>274</v>
       </c>
@@ -11078,11 +10307,8 @@
       <c r="K248">
         <v>80</v>
       </c>
-      <c r="L248">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A249" s="5" t="s">
         <v>275</v>
       </c>
@@ -11116,11 +10342,8 @@
       <c r="K249">
         <v>64</v>
       </c>
-      <c r="L249">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A250" s="5" t="s">
         <v>276</v>
       </c>
@@ -11154,11 +10377,8 @@
       <c r="K250">
         <v>55</v>
       </c>
-      <c r="L250">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A251" s="5" t="s">
         <v>277</v>
       </c>
@@ -11192,11 +10412,8 @@
       <c r="K251">
         <v>57</v>
       </c>
-      <c r="L251">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A252" s="5" t="s">
         <v>278</v>
       </c>
@@ -11230,11 +10447,8 @@
       <c r="K252">
         <v>44</v>
       </c>
-      <c r="L252">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A253" s="5" t="s">
         <v>279</v>
       </c>
@@ -11268,11 +10482,8 @@
       <c r="K253">
         <v>47</v>
       </c>
-      <c r="L253">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A254" s="5" t="s">
         <v>280</v>
       </c>
@@ -11306,11 +10517,8 @@
       <c r="K254">
         <v>5</v>
       </c>
-      <c r="L254">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A255" s="5" t="s">
         <v>281</v>
       </c>
@@ -11344,11 +10552,8 @@
       <c r="K255">
         <v>29</v>
       </c>
-      <c r="L255">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A256" s="5" t="s">
         <v>282</v>
       </c>
@@ -11382,11 +10587,8 @@
       <c r="K256">
         <v>37</v>
       </c>
-      <c r="L256">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A257" s="5" t="s">
         <v>283</v>
       </c>
@@ -11420,11 +10622,8 @@
       <c r="K257">
         <v>26</v>
       </c>
-      <c r="L257">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A258" s="5" t="s">
         <v>284</v>
       </c>
@@ -11458,11 +10657,8 @@
       <c r="K258">
         <v>47</v>
       </c>
-      <c r="L258">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A259" s="5" t="s">
         <v>285</v>
       </c>
@@ -11496,11 +10692,8 @@
       <c r="K259">
         <v>54</v>
       </c>
-      <c r="L259">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A260" s="5" t="s">
         <v>286</v>
       </c>
@@ -11534,11 +10727,8 @@
       <c r="K260">
         <v>65</v>
       </c>
-      <c r="L260">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A261" s="5" t="s">
         <v>287</v>
       </c>
@@ -11572,11 +10762,8 @@
       <c r="K261">
         <v>79</v>
       </c>
-      <c r="L261">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A262" s="5" t="s">
         <v>288</v>
       </c>
@@ -11610,11 +10797,8 @@
       <c r="K262">
         <v>78</v>
       </c>
-      <c r="L262">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A263" s="5" t="s">
         <v>289</v>
       </c>
@@ -11648,11 +10832,8 @@
       <c r="K263">
         <v>60</v>
       </c>
-      <c r="L263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A264" s="5" t="s">
         <v>290</v>
       </c>
@@ -11686,11 +10867,8 @@
       <c r="K264">
         <v>41</v>
       </c>
-      <c r="L264">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A265" s="5" t="s">
         <v>291</v>
       </c>
@@ -11724,11 +10902,8 @@
       <c r="K265">
         <v>45</v>
       </c>
-      <c r="L265">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A266" s="5" t="s">
         <v>292</v>
       </c>
@@ -11762,11 +10937,8 @@
       <c r="K266">
         <v>66</v>
       </c>
-      <c r="L266">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A267" s="5" t="s">
         <v>293</v>
       </c>
@@ -11800,11 +10972,8 @@
       <c r="K267">
         <v>69</v>
       </c>
-      <c r="L267">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A268" s="5" t="s">
         <v>294</v>
       </c>
@@ -11838,11 +11007,8 @@
       <c r="K268">
         <v>69</v>
       </c>
-      <c r="L268">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A269" s="5" t="s">
         <v>295</v>
       </c>
@@ -11876,11 +11042,8 @@
       <c r="K269">
         <v>66</v>
       </c>
-      <c r="L269">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A270" s="5" t="s">
         <v>296</v>
       </c>
@@ -11914,11 +11077,8 @@
       <c r="K270">
         <v>57</v>
       </c>
-      <c r="L270">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A271" s="5" t="s">
         <v>297</v>
       </c>
@@ -11952,11 +11112,8 @@
       <c r="K271">
         <v>73</v>
       </c>
-      <c r="L271">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A272" s="5" t="s">
         <v>298</v>
       </c>
@@ -11990,11 +11147,8 @@
       <c r="K272">
         <v>70</v>
       </c>
-      <c r="L272">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A273" s="5" t="s">
         <v>299</v>
       </c>
@@ -12028,11 +11182,8 @@
       <c r="K273">
         <v>70</v>
       </c>
-      <c r="L273">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A274" s="5" t="s">
         <v>300</v>
       </c>
@@ -12066,11 +11217,8 @@
       <c r="K274">
         <v>7</v>
       </c>
-      <c r="L274">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A275" s="5" t="s">
         <v>301</v>
       </c>
@@ -12104,11 +11252,8 @@
       <c r="K275">
         <v>8</v>
       </c>
-      <c r="L275">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A276" s="5" t="s">
         <v>302</v>
       </c>
@@ -12142,11 +11287,8 @@
       <c r="K276">
         <v>28</v>
       </c>
-      <c r="L276">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A277" s="5" t="s">
         <v>303</v>
       </c>
@@ -12180,11 +11322,8 @@
       <c r="K277">
         <v>16</v>
       </c>
-      <c r="L277">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A278" s="5" t="s">
         <v>304</v>
       </c>
@@ -12218,11 +11357,8 @@
       <c r="K278">
         <v>16</v>
       </c>
-      <c r="L278">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A279" s="5" t="s">
         <v>305</v>
       </c>
@@ -12256,11 +11392,8 @@
       <c r="K279">
         <v>18</v>
       </c>
-      <c r="L279">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A280" s="5" t="s">
         <v>306</v>
       </c>
@@ -12294,11 +11427,8 @@
       <c r="K280">
         <v>51</v>
       </c>
-      <c r="L280">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A281" s="5" t="s">
         <v>307</v>
       </c>
@@ -12332,11 +11462,8 @@
       <c r="K281">
         <v>30</v>
       </c>
-      <c r="L281">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A282" s="5" t="s">
         <v>308</v>
       </c>
@@ -12370,11 +11497,8 @@
       <c r="K282">
         <v>41</v>
       </c>
-      <c r="L282">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A283" s="5" t="s">
         <v>309</v>
       </c>
@@ -12408,11 +11532,8 @@
       <c r="K283">
         <v>32</v>
       </c>
-      <c r="L283">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A284" s="5" t="s">
         <v>310</v>
       </c>
@@ -12446,11 +11567,8 @@
       <c r="K284">
         <v>32</v>
       </c>
-      <c r="L284">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A285" s="5" t="s">
         <v>311</v>
       </c>
@@ -12484,11 +11602,8 @@
       <c r="K285">
         <v>41</v>
       </c>
-      <c r="L285">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A286" s="5" t="s">
         <v>312</v>
       </c>
@@ -12522,11 +11637,8 @@
       <c r="K286">
         <v>41</v>
       </c>
-      <c r="L286">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A287" s="5" t="s">
         <v>313</v>
       </c>
@@ -12560,11 +11672,8 @@
       <c r="K287">
         <v>41</v>
       </c>
-      <c r="L287">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A288" s="5" t="s">
         <v>314</v>
       </c>
@@ -12598,11 +11707,8 @@
       <c r="K288">
         <v>43</v>
       </c>
-      <c r="L288">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A289" s="5" t="s">
         <v>315</v>
       </c>
@@ -12636,11 +11742,8 @@
       <c r="K289">
         <v>37</v>
       </c>
-      <c r="L289">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A290" s="5" t="s">
         <v>316</v>
       </c>
@@ -12674,11 +11777,8 @@
       <c r="K290">
         <v>53</v>
       </c>
-      <c r="L290">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A291" s="5" t="s">
         <v>317</v>
       </c>
@@ -12712,11 +11812,8 @@
       <c r="K291">
         <v>63</v>
       </c>
-      <c r="L291">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A292" s="5" t="s">
         <v>318</v>
       </c>
@@ -12750,11 +11847,8 @@
       <c r="K292">
         <v>59</v>
       </c>
-      <c r="L292">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A293" s="5" t="s">
         <v>319</v>
       </c>
@@ -12788,11 +11882,8 @@
       <c r="K293">
         <v>59</v>
       </c>
-      <c r="L293">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A294" s="5" t="s">
         <v>320</v>
       </c>
@@ -12826,11 +11917,8 @@
       <c r="K294">
         <v>51</v>
       </c>
-      <c r="L294">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A295" s="5" t="s">
         <v>321</v>
       </c>
@@ -12864,11 +11952,8 @@
       <c r="K295">
         <v>46</v>
       </c>
-      <c r="L295">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A296" s="5" t="s">
         <v>322</v>
       </c>
@@ -12902,11 +11987,8 @@
       <c r="K296">
         <v>41</v>
       </c>
-      <c r="L296">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A297" s="5" t="s">
         <v>323</v>
       </c>
@@ -12940,11 +12022,8 @@
       <c r="K297">
         <v>58</v>
       </c>
-      <c r="L297">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A298" s="5" t="s">
         <v>324</v>
       </c>
@@ -12977,9 +12056,6 @@
       </c>
       <c r="K298">
         <v>60</v>
-      </c>
-      <c r="L298">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13822,39 +12898,17 @@
       <c r="A1" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>336</v>
-      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
